--- a/Nifty50Stocks_QtyResultDates.xlsx
+++ b/Nifty50Stocks_QtyResultDates.xlsx
@@ -21,9 +21,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -3964,16 +3963,16 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Hero MotoCorp Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>45875</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="22">
@@ -4024,16 +4023,16 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>45866</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="26">
@@ -4309,12 +4308,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Tata Motors Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="C44" s="10" t="n">
